--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -14555,6 +14555,275 @@
         </ns0:is>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="239" spans="1:16">
+      <ns0:c r="A239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>九蓮寶燈</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>一万年老海妖</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Uka</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>5071</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G239" s="8">
+        <ns0:v>7.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>5071</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I239" s="8">
+        <ns0:v>10.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="J239" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Leadlink rev. qqx &amp; rchr</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K239" s="8">
+        <ns0:v>12.9</ns0:v>
+      </ns0:c>
+      <ns0:c r="P239" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Nine Lights</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="240" spans="1:16">
+      <ns0:c r="A240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Cyber Attack</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Xeudo Code</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>干尸肥皂</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>C_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G240" s="8">
+        <ns0:v>4.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>L_2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I240" s="8">
+        <ns0:v>8.1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J240" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>E_3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K240" s="8">
+        <ns0:v>12.4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="241" spans="1:16">
+      <ns0:c r="A241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Ark</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>kanoryo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Calics</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>M-Ark-X-3957</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G241" s="8">
+        <ns0:v>4.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>M-Ark-X-3957</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I241" s="8">
+        <ns0:v>8.1</ns0:v>
+      </ns0:c>
+      <ns0:c r="J241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Max3957~The Navigator</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K241" s="8">
+        <ns0:v>11.9</ns0:v>
+      </ns0:c>
+      <ns0:c r="L241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RUIN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M241" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MDTT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N241" s="8">
+        <ns0:v>13.0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="242" spans="1:16">
+      <ns0:c r="A242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Qamar</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>星咲Suzumi</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Co2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LOAO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G242" s="8">
+        <ns0:v>5.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LOAO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I242" s="8">
+        <ns0:v>9.3</ns0:v>
+      </ns0:c>
+      <ns0:c r="J242" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LOAO vs qqxqqx vs Nyo</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K242" s="8">
+        <ns0:v>12.0</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="243" spans="1:16">
+      <ns0:c r="A243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Fuzzy-Navel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>わかどり</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>もがみ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ICEbluebee_</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G243" s="8">
+        <ns0:v>4.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ICEbluebee_</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I243" s="8">
+        <ns0:v>8.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="J243" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ICEbluebee_</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K243" s="8">
+        <ns0:v>11.6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="244" spans="1:16">
+      <ns0:c r="A244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FRENZY☆SHINY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>D·ENNY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>干尸肥皂</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>-X</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G244" s="8">
+        <ns0:v>2.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>-X</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I244" s="8">
+        <ns0:v>6.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="J244" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>三味之星*Q.O.X</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K244" s="8">
+        <ns0:v>11.3</ns0:v>
+      </ns0:c>
+      <ns0:c r="P244" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FRENZYaSHINY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:N239">
     <ns0:sortState ref="A2:N239">

--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -1218,20 +1218,35 @@
       </ns0:c>
       <ns0:c r="L1" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>追加谱面</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>追加谱面谱师</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="N1" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>追加谱面难度</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="P1" s="0" t="inlineStr">
+          <ns0:t xml:space="preserve">RUIN谱面谱师</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M1" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">RUIN谱面难度</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">DREAMY谱面谱师</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O1" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">DREAMY谱面难度</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">FOOL谱面谱师</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q1" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">FOOL谱面难度</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R1" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>别名</ns0:t>
         </ns0:is>
@@ -1287,7 +1302,7 @@
       <ns0:c r="K2" s="8" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="P2" s="0" t="inlineStr">
+      <ns0:c r="R2" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>HELP</ns0:t>
         </ns0:is>
@@ -1343,7 +1358,7 @@
       <ns0:c r="K3" s="8" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="P3" s="0" t="inlineStr">
+      <ns0:c r="R3" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Time Shine</ns0:t>
         </ns0:is>
@@ -1383,7 +1398,7 @@
       <ns0:c r="K4" s="8" t="n">
         <ns0:v>7.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P4" s="0" t="inlineStr">
+      <ns0:c r="R4" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Water Fairy</ns0:t>
         </ns0:is>
@@ -1439,7 +1454,7 @@
       <ns0:c r="K5" s="8" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="P5" s="0" t="inlineStr">
+      <ns0:c r="R5" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Where   the    Dragons   Live</ns0:t>
         </ns0:is>
@@ -1496,7 +1511,7 @@
       <ns0:c r="K6" s="8" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="P6" t="inlineStr">
+      <ns0:c r="R6" t="inlineStr">
         <ns0:is>
           <ns0:t>The End Girl</ns0:t>
         </ns0:is>
@@ -1605,18 +1620,13 @@
       </ns0:c>
       <ns0:c r="L8" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M8" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>nyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N8" s="8" t="n">
+      <ns0:c r="M8" s="8" t="n">
         <ns0:v>12.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P8" s="0" t="inlineStr">
+      <ns0:c r="R8" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Light and Color</ns0:t>
         </ns0:is>
@@ -1674,18 +1684,13 @@
       </ns0:c>
       <ns0:c r="L9" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M9" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>O-Ω-∅ feat.Akino Respect For Χμονγβ.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N9" s="8" t="n">
+      <ns0:c r="M9" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P9" s="0" t="inlineStr">
+      <ns0:c r="R9" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Untrodden   Morn</ns0:t>
         </ns0:is>
@@ -1843,7 +1848,7 @@
       <ns0:c r="K12" s="8" t="n">
         <ns0:v>9.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P12" s="0" t="inlineStr">
+      <ns0:c r="R12" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>small DENG kitchen</ns0:t>
         </ns0:is>
@@ -1901,15 +1906,10 @@
       </ns0:c>
       <ns0:c r="L13" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M13" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N13" s="8" t="n">
+      <ns0:c r="M13" s="8" t="n">
         <ns0:v>11.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -2009,7 +2009,7 @@
       <ns0:c r="K15" s="8" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="P15" s="0" t="inlineStr">
+      <ns0:c r="R15" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Winter Cube</ns0:t>
         </ns0:is>
@@ -2065,7 +2065,17 @@
       <ns0:c r="K16" s="8" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="P16" s="0" t="inlineStr">
+      <ns0:c r="N16" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Code_2110_N.Y.O.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O16" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">割(0.001)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R16" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Voice meaning</ns0:t>
         </ns0:is>
@@ -2121,7 +2131,7 @@
       <ns0:c r="K17" s="8" t="n">
         <ns0:v>10.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P17" s="0" t="inlineStr">
+      <ns0:c r="R17" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>kakuriyo dancehall</ns0:t>
         </ns0:is>
@@ -2177,7 +2187,7 @@
       <ns0:c r="K18" s="8" t="n">
         <ns0:v>10.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P18" s="0" t="inlineStr">
+      <ns0:c r="R18" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>lucid trigger</ns0:t>
         </ns0:is>
@@ -2233,7 +2243,7 @@
       <ns0:c r="K19" s="8" t="n">
         <ns0:v>10.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P19" s="0" t="inlineStr">
+      <ns0:c r="R19" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Double Life</ns0:t>
         </ns0:is>
@@ -2289,7 +2299,7 @@
       <ns0:c r="K20" s="8" t="n">
         <ns0:v>10.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P20" s="0" t="inlineStr">
+      <ns0:c r="R20" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>The Shape of Smiles</ns0:t>
         </ns0:is>
@@ -2345,7 +2355,7 @@
       <ns0:c r="K21" s="8" t="n">
         <ns0:v>10.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P21" s="0" t="inlineStr">
+      <ns0:c r="R21" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>lian</ns0:t>
         </ns0:is>
@@ -2403,18 +2413,13 @@
       </ns0:c>
       <ns0:c r="L22" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M22" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>⚠WARNING⚠</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N22" s="8" t="n">
+      <ns0:c r="M22" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P22" s="0" t="inlineStr">
+      <ns0:c r="R22" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>The   Mountain   Eater</ns0:t>
         </ns0:is>
@@ -2466,15 +2471,10 @@
       </ns0:c>
       <ns0:c r="L23" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M23" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>oowoooowoo feat.Koutarou</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N23" s="8" t="n">
+      <ns0:c r="M23" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -2579,7 +2579,7 @@
       <ns0:c r="K25" s="8" t="n">
         <ns0:v>10.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P25" s="0" t="inlineStr">
+      <ns0:c r="R25" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>love_in_adversity</ns0:t>
         </ns0:is>
@@ -2738,7 +2738,7 @@
       <ns0:c r="K28" s="8" t="n">
         <ns0:v>10.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P28" s="0" t="inlineStr">
+      <ns0:c r="R28" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Time To Night Sky</ns0:t>
         </ns0:is>
@@ -2796,18 +2796,13 @@
       </ns0:c>
       <ns0:c r="L29" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M29" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>*Best Wish*</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N29" s="8" t="n">
+      <ns0:c r="M29" s="8" t="n">
         <ns0:v>11.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P29" s="0" t="inlineStr">
+      <ns0:c r="R29" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Star Wish</ns0:t>
         </ns0:is>
@@ -2909,7 +2904,7 @@
       <ns0:c r="K31" s="8" t="n">
         <ns0:v>10.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P31" s="0" t="inlineStr">
+      <ns0:c r="R31" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Today is not tomorrow</ns0:t>
         </ns0:is>
@@ -2965,7 +2960,7 @@
       <ns0:c r="K32" s="8" t="n">
         <ns0:v>10.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P32" s="0" t="inlineStr">
+      <ns0:c r="R32" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Twin Nebula</ns0:t>
         </ns0:is>
@@ -3015,7 +3010,7 @@
       <ns0:c r="K33" s="8" t="n">
         <ns0:v>10.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P33" s="0" t="inlineStr">
+      <ns0:c r="R33" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>ASTRONYAUT</ns0:t>
         </ns0:is>
@@ -3071,7 +3066,7 @@
       <ns0:c r="K34" s="8" t="n">
         <ns0:v>10.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P34" s="0" t="inlineStr">
+      <ns0:c r="R34" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Hush</ns0:t>
         </ns0:is>
@@ -3121,7 +3116,7 @@
       <ns0:c r="K35" s="8" t="n">
         <ns0:v>10.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P35" s="0" t="inlineStr">
+      <ns0:c r="R35" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Try Bass</ns0:t>
         </ns0:is>
@@ -3177,7 +3172,7 @@
       <ns0:c r="K36" s="8" t="n">
         <ns0:v>10.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P36" s="0" t="inlineStr">
+      <ns0:c r="R36" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Galaxy</ns0:t>
         </ns0:is>
@@ -3233,7 +3228,7 @@
       <ns0:c r="K37" s="8" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="P37" s="0" t="inlineStr">
+      <ns0:c r="R37" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>devotion</ns0:t>
         </ns0:is>
@@ -3438,15 +3433,10 @@
       </ns0:c>
       <ns0:c r="L41" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M41" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Nocturyn</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N41" s="8" t="n">
+      <ns0:c r="M41" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -3500,7 +3490,7 @@
       <ns0:c r="K42" s="8" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="P42" s="0" t="inlineStr">
+      <ns0:c r="R42" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>The_Fungus_Dandy</ns0:t>
         </ns0:is>
@@ -3552,15 +3542,10 @@
       </ns0:c>
       <ns0:c r="L43" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M43" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Creeper_001 &amp; qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N43" s="8" t="n">
+      <ns0:c r="M43" s="8" t="n">
         <ns0:v>13.5</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -3665,7 +3650,7 @@
       <ns0:c r="K45" s="8" t="n">
         <ns0:v>11.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P45" s="0" t="inlineStr">
+      <ns0:c r="R45" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>sol guo</ns0:t>
         </ns0:is>
@@ -3772,7 +3757,7 @@
       <ns0:c r="K47" s="8" t="n">
         <ns0:v>11.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P47" s="0" t="inlineStr">
+      <ns0:c r="R47" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Starry Sky Travel</ns0:t>
         </ns0:is>
@@ -3829,7 +3814,7 @@
       <ns0:c r="K48" s="8" t="n">
         <ns0:v>11.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P48" s="0" t="inlineStr">
+      <ns0:c r="R48" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Evil nun</ns0:t>
         </ns0:is>
@@ -3936,7 +3921,7 @@
       <ns0:c r="K50" s="8" t="n">
         <ns0:v>11.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P50" s="0" t="inlineStr">
+      <ns0:c r="R50" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>The Echo of Peach Color</ns0:t>
         </ns0:is>
@@ -3992,7 +3977,7 @@
       <ns0:c r="K51" s="8" t="n">
         <ns0:v>11.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P51" s="0" t="inlineStr">
+      <ns0:c r="R51" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Anokumene</ns0:t>
         </ns0:is>
@@ -4050,18 +4035,13 @@
       </ns0:c>
       <ns0:c r="L52" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M52" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>EggplΔnt³ vs. rIchΔrD³</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N52" s="8" t="n">
+      <ns0:c r="M52" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P52" s="0" t="inlineStr">
+      <ns0:c r="R52" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Cuvism3</ns0:t>
         </ns0:is>
@@ -4119,15 +4099,10 @@
       </ns0:c>
       <ns0:c r="L53" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M53" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Creeper_001 meet qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N53" s="8" t="n">
+      <ns0:c r="M53" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -4222,15 +4197,10 @@
       </ns0:c>
       <ns0:c r="L55" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M55" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>oowoooowoo &amp; feat.Xian &amp; Koutarou</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N55" s="8" t="n">
+      <ns0:c r="M55" s="8" t="n">
         <ns0:v>12.6</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -4335,7 +4305,7 @@
       <ns0:c r="K57" s="8" t="n">
         <ns0:v>11.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P57" s="0" t="inlineStr">
+      <ns0:c r="R57" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Nick   of   Time</ns0:t>
         </ns0:is>
@@ -4393,7 +4363,7 @@
       <ns0:c r="K58" s="8" t="n">
         <ns0:v>11.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P58" s="0" t="inlineStr">
+      <ns0:c r="R58" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>noctilucent_moon</ns0:t>
         </ns0:is>
@@ -4451,15 +4421,10 @@
       </ns0:c>
       <ns0:c r="L59" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M59" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Nyo（白の物语）</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N59" s="8" t="n">
+      <ns0:c r="M59" s="8" t="n">
         <ns0:v>11.6</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -4509,7 +4474,7 @@
       <ns0:c r="K60" s="8" t="n">
         <ns0:v>11.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P60" s="0" t="inlineStr">
+      <ns0:c r="R60" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Reason_Of_Fallen</ns0:t>
         </ns0:is>
@@ -4567,18 +4532,13 @@
       </ns0:c>
       <ns0:c r="L61" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M61" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N61" s="8" t="n">
+      <ns0:c r="M61" s="8" t="n">
         <ns0:v>11.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P61" s="0" t="inlineStr">
+      <ns0:c r="R61" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>dopedopedope</ns0:t>
         </ns0:is>
@@ -4787,7 +4747,7 @@
       <ns0:c r="K65" s="8" t="n">
         <ns0:v>11.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P65" s="0" t="inlineStr">
+      <ns0:c r="R65" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Scheelite</ns0:t>
         </ns0:is>
@@ -4843,7 +4803,7 @@
       <ns0:c r="K66" s="8" t="n">
         <ns0:v>11.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P66" s="0" t="inlineStr">
+      <ns0:c r="R66" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Euenching</ns0:t>
         </ns0:is>
@@ -4951,7 +4911,7 @@
       <ns0:c r="K68" s="8" t="n">
         <ns0:v>11.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P68" s="0" t="inlineStr">
+      <ns0:c r="R68" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Ether Vortex</ns0:t>
         </ns0:is>
@@ -5052,15 +5012,10 @@
       </ns0:c>
       <ns0:c r="L70" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M70" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙包aa</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N70" s="8" t="n">
+      <ns0:c r="M70" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -5114,7 +5069,7 @@
       <ns0:c r="K71" s="8" t="n">
         <ns0:v>11.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P71" s="0" t="inlineStr">
+      <ns0:c r="R71" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Wild   Dances</ns0:t>
         </ns0:is>
@@ -5166,18 +5121,13 @@
       </ns0:c>
       <ns0:c r="L72" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M72" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>kira</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N72" s="8" t="n">
+      <ns0:c r="M72" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P72" s="0" t="inlineStr">
+      <ns0:c r="R72" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Six Light Bird</ns0:t>
         </ns0:is>
@@ -5329,7 +5279,7 @@
       <ns0:c r="K75" s="8" t="n">
         <ns0:v>11.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P75" s="0" t="inlineStr">
+      <ns0:c r="R75" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Qlifact</ns0:t>
         </ns0:is>
@@ -5385,7 +5335,7 @@
       <ns0:c r="K76" s="8" t="n">
         <ns0:v>11.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P76" s="0" t="inlineStr">
+      <ns0:c r="R76" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Pouring white soup on the piano</ns0:t>
         </ns0:is>
@@ -5441,7 +5391,7 @@
       <ns0:c r="K77" s="8" t="n">
         <ns0:v>11.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P77" s="0" t="inlineStr">
+      <ns0:c r="R77" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Dream   Hard   Find</ns0:t>
         </ns0:is>
@@ -5550,15 +5500,10 @@
       </ns0:c>
       <ns0:c r="L79" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M79" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx vs. Nyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N79" s="8" t="n">
+      <ns0:c r="M79" s="8" t="n">
         <ns0:v>12.6</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -5716,15 +5661,10 @@
       </ns0:c>
       <ns0:c r="L82" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M82" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>OOWOOOOWOO feat.O-Ω-∅</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N82" s="8" t="n">
+      <ns0:c r="M82" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -5823,7 +5763,7 @@
       <ns0:c r="K84" s="8" t="n">
         <ns0:v>11.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P84" s="0" t="inlineStr">
+      <ns0:c r="R84" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Niflhel</ns0:t>
         </ns0:is>
@@ -6032,7 +5972,7 @@
       <ns0:c r="K88" s="8" t="n">
         <ns0:v>11.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P88" s="0" t="inlineStr">
+      <ns0:c r="R88" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>find me</ns0:t>
         </ns0:is>
@@ -6237,15 +6177,10 @@
       </ns0:c>
       <ns0:c r="L92" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M92" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>||/||/</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N92" s="8" t="n">
+      <ns0:c r="M92" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -6301,18 +6236,13 @@
       </ns0:c>
       <ns0:c r="L93" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M93" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N93" s="8" t="n">
+      <ns0:c r="M93" s="8" t="n">
         <ns0:v>12.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P93" s="0" t="inlineStr">
+      <ns0:c r="R93" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>raina</ns0:t>
         </ns0:is>
@@ -6370,18 +6300,13 @@
       </ns0:c>
       <ns0:c r="L94" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M94" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>ƎMALFTƧOЯF</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N94" s="8" t="n">
+      <ns0:c r="M94" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P94" s="0" t="inlineStr">
+      <ns0:c r="R94" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>mirror shadow</ns0:t>
         </ns0:is>
@@ -6431,22 +6356,17 @@
       <ns0:c r="K95" s="8" t="n">
         <ns0:v>11.7</ns0:v>
       </ns0:c>
-      <ns0:c r="L95" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M95" s="1" t="inlineStr">
+      <ns0:c r="N95" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>q  q x q q  x</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N95" s="8" t="inlineStr">
+      <ns0:c r="O95" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>α(0.001)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P95" s="0" t="inlineStr">
+      <ns0:c r="R95" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>catalyzer</ns0:t>
         </ns0:is>
@@ -6504,15 +6424,10 @@
       </ns0:c>
       <ns0:c r="L96" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M96" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>creeper_001 meet qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N96" s="8" t="n">
+      <ns0:c r="M96" s="8" t="n">
         <ns0:v>13.4</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -6619,15 +6534,10 @@
       </ns0:c>
       <ns0:c r="L98" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M98" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N98" s="8" t="n">
+      <ns0:c r="M98" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -6682,7 +6592,7 @@
       <ns0:c r="K99" s="8" t="n">
         <ns0:v>11.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P99" s="0" t="inlineStr">
+      <ns0:c r="R99" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>my heaven</ns0:t>
         </ns0:is>
@@ -6738,7 +6648,7 @@
       <ns0:c r="K100" s="8" t="n">
         <ns0:v>11.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P100" s="0" t="inlineStr">
+      <ns0:c r="R100" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>sad dragon</ns0:t>
         </ns0:is>
@@ -6839,7 +6749,7 @@
       <ns0:c r="K102" s="8" t="n">
         <ns0:v>11.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P102" s="0" t="inlineStr">
+      <ns0:c r="R102" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Storm Dance</ns0:t>
         </ns0:is>
@@ -7169,22 +7079,17 @@
       <ns0:c r="K109" s="8" t="n">
         <ns0:v>11.9</ns0:v>
       </ns0:c>
-      <ns0:c r="L109" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M109" s="1" t="inlineStr">
+      <ns0:c r="N109" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N109" s="8" t="inlineStr">
+      <ns0:c r="O109" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>β(0.001)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P109" s="0" t="inlineStr">
+      <ns0:c r="R109" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Silver   Town</ns0:t>
         </ns0:is>
@@ -7232,7 +7137,7 @@
       <ns0:c r="K110" s="8" t="n">
         <ns0:v>11.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P110" s="0" t="inlineStr">
+      <ns0:c r="R110" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>dragen north</ns0:t>
         </ns0:is>
@@ -7288,7 +7193,7 @@
       <ns0:c r="K111" s="8" t="n">
         <ns0:v>11.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P111" s="0" t="inlineStr">
+      <ns0:c r="R111" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>girl writer</ns0:t>
         </ns0:is>
@@ -7334,18 +7239,13 @@
       </ns0:c>
       <ns0:c r="L112" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M112" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>LudwigVanqqx vs. LudwigVanNyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N112" s="8" t="n">
+      <ns0:c r="M112" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="P112" s="0" t="inlineStr">
+      <ns0:c r="R112" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Moonlight</ns0:t>
         </ns0:is>
@@ -7403,18 +7303,13 @@
       </ns0:c>
       <ns0:c r="L113" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M113" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Quetzal X</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N113" s="8" t="n">
+      <ns0:c r="M113" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="P113" s="0" t="inlineStr">
+      <ns0:c r="R113" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>bossfire</ns0:t>
         </ns0:is>
@@ -7470,7 +7365,7 @@
       <ns0:c r="K114" s="8" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="P114" s="0" t="inlineStr">
+      <ns0:c r="R114" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Bright Red Hertz</ns0:t>
         </ns0:is>
@@ -7675,15 +7570,10 @@
       </ns0:c>
       <ns0:c r="L118" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M118" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>rIchArD × 霜炎</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N118" s="8" t="n">
+      <ns0:c r="M118" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -7782,7 +7672,7 @@
       <ns0:c r="K120" s="8" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="P120" s="0" t="inlineStr">
+      <ns0:c r="R120" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>car girl</ns0:t>
         </ns0:is>
@@ -7826,7 +7716,7 @@
       <ns0:c r="K121" s="8" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="P121" s="0" t="inlineStr">
+      <ns0:c r="R121" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Crimson Masquerade</ns0:t>
         </ns0:is>
@@ -8082,15 +7972,10 @@
       </ns0:c>
       <ns0:c r="L126" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M126" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>miSERable</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N126" s="8" t="n">
+      <ns0:c r="M126" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8338,18 +8223,13 @@
       </ns0:c>
       <ns0:c r="L131" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M131" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>BZG9999 with LeadLink</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N131" s="8" t="n">
+      <ns0:c r="M131" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P131" s="0" t="inlineStr">
+      <ns0:c r="R131" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Firmament   Star</ns0:t>
         </ns0:is>
@@ -8458,15 +8338,10 @@
       </ns0:c>
       <ns0:c r="L133" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M133" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>OOωOO</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N133" s="8" t="n">
+      <ns0:c r="M133" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8522,18 +8397,13 @@
       </ns0:c>
       <ns0:c r="L134" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M134" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>?Owo!_WH</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N134" s="8" t="n">
+      <ns0:c r="M134" s="8" t="n">
         <ns0:v>13.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P134" s="0" t="inlineStr">
+      <ns0:c r="R134" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>MIRROR</ns0:t>
         </ns0:is>
@@ -8591,15 +8461,10 @@
       </ns0:c>
       <ns0:c r="L135" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M135" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>OOWOOOOWOO</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N135" s="8" t="n">
+      <ns0:c r="M135" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8645,7 +8510,7 @@
       <ns0:c r="K136" s="8" t="n">
         <ns0:v>12.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P136" s="0" t="inlineStr">
+      <ns0:c r="R136" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Eternal Wings</ns0:t>
         </ns0:is>
@@ -8703,15 +8568,10 @@
       </ns0:c>
       <ns0:c r="L137" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M137" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙包aaa. vs.Null1ty_</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N137" s="8" t="n">
+      <ns0:c r="M137" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8761,15 +8621,10 @@
       </ns0:c>
       <ns0:c r="L138" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M138" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>OOWOOOOWOO</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N138" s="8" t="n">
+      <ns0:c r="M138" s="8" t="n">
         <ns0:v>12.6</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8823,6 +8678,16 @@
       <ns0:c r="K139" s="8" t="n">
         <ns0:v>12.3</ns0:v>
       </ns0:c>
+      <ns0:c r="N139" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">I'll be CREEEEEEEEING day and night!!!</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O139" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">狂(0.001)</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="140">
       <ns0:c r="A140" s="6" t="inlineStr">
@@ -8876,15 +8741,10 @@
       </ns0:c>
       <ns0:c r="L140" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M140" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>The Melody for You</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N140" s="8" t="n">
+      <ns0:c r="M140" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -8932,7 +8792,7 @@
       <ns0:c r="K141" s="8" t="n">
         <ns0:v>12.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P141" s="0" t="inlineStr">
+      <ns0:c r="R141" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Once_Again</ns0:t>
         </ns0:is>
@@ -8988,7 +8848,7 @@
       <ns0:c r="K142" s="8" t="n">
         <ns0:v>12.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P142" s="0" t="inlineStr">
+      <ns0:c r="R142" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>REVOCATE</ns0:t>
         </ns0:is>
@@ -9093,15 +8953,10 @@
       </ns0:c>
       <ns0:c r="L144" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M144" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙包aa vs.Quetzal X</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N144" s="8" t="n">
+      <ns0:c r="M144" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -9149,7 +9004,7 @@
       <ns0:c r="K145" s="8" t="n">
         <ns0:v>12.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P145" s="0" t="inlineStr">
+      <ns0:c r="R145" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>ReNatus</ns0:t>
         </ns0:is>
@@ -9205,7 +9060,7 @@
       <ns0:c r="K146" s="8" t="n">
         <ns0:v>12.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P146" s="0" t="inlineStr">
+      <ns0:c r="R146" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>FengYa</ns0:t>
         </ns0:is>
@@ -9263,18 +9118,13 @@
       </ns0:c>
       <ns0:c r="L147" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M147" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙包aaa[Registed]</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N147" s="8" t="n">
+      <ns0:c r="M147" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P147" s="0" t="inlineStr">
+      <ns0:c r="R147" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>register_fantobia</ns0:t>
         </ns0:is>
@@ -9383,18 +9233,13 @@
       </ns0:c>
       <ns0:c r="L149" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M149" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>ずっと小理でいいのに</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N149" s="8" t="n">
+      <ns0:c r="M149" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P149" s="0" t="inlineStr">
+      <ns0:c r="R149" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>StellapphireM</ns0:t>
         </ns0:is>
@@ -9501,7 +9346,7 @@
       <ns0:c r="K151" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P151" s="0" t="inlineStr">
+      <ns0:c r="R151" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>CATACLYSM</ns0:t>
         </ns0:is>
@@ -9661,15 +9506,10 @@
       </ns0:c>
       <ns0:c r="L154" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M154" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>XScnaem</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N154" s="8" t="n">
+      <ns0:c r="M154" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -9723,7 +9563,7 @@
       <ns0:c r="K155" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P155" s="0" t="inlineStr">
+      <ns0:c r="R155" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Flaming   Heart</ns0:t>
         </ns0:is>
@@ -9881,7 +9721,7 @@
       <ns0:c r="K158" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
-      <ns0:c r="P158" s="0" t="inlineStr">
+      <ns0:c r="R158" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Magic Sink</ns0:t>
         </ns0:is>
@@ -9929,17 +9769,12 @@
       <ns0:c r="K159" s="8" t="n">
         <ns0:v>12.4</ns0:v>
       </ns0:c>
-      <ns0:c r="L159" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M159" s="1" t="inlineStr">
+      <ns0:c r="N159" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Disable-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N159" s="8" t="inlineStr">
+      <ns0:c r="O159" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>γ(0.001)</ns0:t>
         </ns0:is>
@@ -10048,15 +9883,10 @@
       </ns0:c>
       <ns0:c r="L161" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M161" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>XIAN</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N161" s="8" t="n">
+      <ns0:c r="M161" s="8" t="n">
         <ns0:v>13.7</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -10110,7 +9940,7 @@
       <ns0:c r="K162" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P162" s="0" t="inlineStr">
+      <ns0:c r="R162" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>csqn</ns0:t>
         </ns0:is>
@@ -10168,15 +9998,10 @@
       </ns0:c>
       <ns0:c r="L163" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M163" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>[qqxqqx]-[Creeper_001]-[Nyo]</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N163" s="8" t="n">
+      <ns0:c r="M163" s="8" t="n">
         <ns0:v>13.5</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -10232,15 +10057,10 @@
       </ns0:c>
       <ns0:c r="L164" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M164" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙包aaa</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N164" s="8" t="n">
+      <ns0:c r="M164" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -10295,7 +10115,7 @@
       <ns0:c r="K165" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P165" s="0" t="inlineStr">
+      <ns0:c r="R165" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>infinite domination</ns0:t>
         </ns0:is>
@@ -10351,22 +10171,17 @@
       <ns0:c r="K166" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="L166" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M166" s="1" t="inlineStr">
+      <ns0:c r="N166" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N166" s="8" t="inlineStr">
+      <ns0:c r="O166" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>γ(0.001)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P166" s="0" t="inlineStr">
+      <ns0:c r="R166" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Let's get wild</ns0:t>
         </ns0:is>
@@ -10424,15 +10239,10 @@
       </ns0:c>
       <ns0:c r="L167" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M167" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>The-Legend-Teller Nocturyn</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N167" s="8" t="n">
+      <ns0:c r="M167" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -10486,7 +10296,7 @@
       <ns0:c r="K168" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P168" s="0" t="inlineStr">
+      <ns0:c r="R168" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>SONIC SURGE</ns0:t>
         </ns0:is>
@@ -10595,18 +10405,13 @@
       </ns0:c>
       <ns0:c r="L170" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M170" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>xian</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N170" s="8" t="n">
+      <ns0:c r="M170" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="P170" s="0" t="inlineStr">
+      <ns0:c r="R170" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>The pattern of Neve</ns0:t>
         </ns0:is>
@@ -10664,18 +10469,13 @@
       </ns0:c>
       <ns0:c r="L171" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M171" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Quetzal X</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N171" s="8" t="n">
+      <ns0:c r="M171" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P171" s="0" t="inlineStr">
+      <ns0:c r="R171" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>StormWillow</ns0:t>
         </ns0:is>
@@ -10833,7 +10633,7 @@
       <ns0:c r="K174" s="8" t="n">
         <ns0:v>12.5</ns0:v>
       </ns0:c>
-      <ns0:c r="P174" s="0" t="inlineStr">
+      <ns0:c r="R174" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Eyes Zero</ns0:t>
         </ns0:is>
@@ -10942,15 +10742,10 @@
       </ns0:c>
       <ns0:c r="L176" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M176" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>!?xqBByo?!</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N176" s="8" t="n">
+      <ns0:c r="M176" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -10996,7 +10791,7 @@
       <ns0:c r="K177" s="8" t="n">
         <ns0:v>12.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P177" s="0" t="inlineStr">
+      <ns0:c r="R177" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>BinaryWonderland</ns0:t>
         </ns0:is>
@@ -11150,15 +10945,10 @@
       </ns0:c>
       <ns0:c r="L180" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M180" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>999qqxianer</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N180" s="8" t="n">
+      <ns0:c r="M180" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11214,15 +11004,10 @@
       </ns0:c>
       <ns0:c r="L181" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M181" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Deasutone_WH</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N181" s="8" t="n">
+      <ns0:c r="M181" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11425,15 +11210,10 @@
       </ns0:c>
       <ns0:c r="L185" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M185" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Creeper_001 ＆ qqxqqx</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N185" s="8" t="n">
+      <ns0:c r="M185" s="8" t="n">
         <ns0:v>13.5</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11489,18 +11269,13 @@
       </ns0:c>
       <ns0:c r="L186" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M186" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>MAHOU~Remaine_WH~'s ReBirth</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N186" s="8" t="n">
+      <ns0:c r="M186" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P186" s="0" t="inlineStr">
+      <ns0:c r="R186" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Iron-Blooded Witch</ns0:t>
         </ns0:is>
@@ -11609,15 +11384,10 @@
       </ns0:c>
       <ns0:c r="L188" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M188" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>BETWEEN THE TRUTH.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N188" s="8" t="n">
+      <ns0:c r="M188" s="8" t="n">
         <ns0:v>13.7</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11673,15 +11443,10 @@
       </ns0:c>
       <ns0:c r="L189" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M189" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Quetzal X</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N189" s="8" t="n">
+      <ns0:c r="M189" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11788,15 +11553,10 @@
       </ns0:c>
       <ns0:c r="L191" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M191" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx feat.WH</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N191" s="8" t="n">
+      <ns0:c r="M191" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -11851,7 +11611,7 @@
       <ns0:c r="K192" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P192" s="0" t="inlineStr">
+      <ns0:c r="R192" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>atruthseeker</ns0:t>
         </ns0:is>
@@ -12011,15 +11771,10 @@
       </ns0:c>
       <ns0:c r="L195" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M195" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>The Duke of Demons : OOMOO</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N195" s="8" t="n">
+      <ns0:c r="M195" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12122,22 +11877,17 @@
       <ns0:c r="K197" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="L197" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>FOOL</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M197" s="1" t="inlineStr">
+      <ns0:c r="P197" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>SLIDE MASTER -0A0-</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N197" s="8" t="inlineStr">
+      <ns0:c r="Q197" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>-45(0.0)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P197" s="0" t="inlineStr">
+      <ns0:c r="R197" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Gengaozo</ns0:t>
         </ns0:is>
@@ -12195,15 +11945,10 @@
       </ns0:c>
       <ns0:c r="L198" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M198" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx VS. OOWOOOOWOO</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N198" s="8" t="n">
+      <ns0:c r="M198" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12257,7 +12002,7 @@
       <ns0:c r="K199" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P199" s="0" t="inlineStr">
+      <ns0:c r="R199" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>M3F2_X</ns0:t>
         </ns0:is>
@@ -12358,7 +12103,7 @@
       <ns0:c r="K201" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P201" s="0" t="inlineStr">
+      <ns0:c r="R201" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Lacertid</ns0:t>
         </ns0:is>
@@ -12410,18 +12155,13 @@
       </ns0:c>
       <ns0:c r="L202" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M202" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>豆沙馅超新星(豆沙包aaa＆SN2018zd) ＋ 鹊桥馅苦力怕（qqxqqx＆Creeper_001)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N202" s="8" t="n">
+      <ns0:c r="M202" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P202" s="0" t="inlineStr">
+      <ns0:c r="R202" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Dancer of the End</ns0:t>
         </ns0:is>
@@ -12479,18 +12219,13 @@
       </ns0:c>
       <ns0:c r="L203" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M203" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Quetzal X</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N203" s="8" t="n">
+      <ns0:c r="M203" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P203" s="0" t="inlineStr">
+      <ns0:c r="R203" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Myth Compiler</ns0:t>
         </ns0:is>
@@ -12546,7 +12281,7 @@
       <ns0:c r="K204" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P204" s="0" t="inlineStr">
+      <ns0:c r="R204" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Re_Start</ns0:t>
         </ns0:is>
@@ -12604,15 +12339,10 @@
       </ns0:c>
       <ns0:c r="L205" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M205" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx feat.oowoooowoo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N205" s="8" t="n">
+      <ns0:c r="M205" s="8" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12668,15 +12398,10 @@
       </ns0:c>
       <ns0:c r="L206" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M206" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqx ＆ owo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N206" s="8" t="n">
+      <ns0:c r="M206" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12730,7 +12455,7 @@
       <ns0:c r="K207" s="8" t="n">
         <ns0:v>12.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P207" s="0" t="inlineStr">
+      <ns0:c r="R207" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Infinity</ns0:t>
         </ns0:is>
@@ -12782,15 +12507,10 @@
       </ns0:c>
       <ns0:c r="L208" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M208" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Nap vs. FemtS feat. MDTT</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N208" s="8" t="n">
+      <ns0:c r="M208" s="8" t="n">
         <ns0:v>13.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12846,18 +12566,13 @@
       </ns0:c>
       <ns0:c r="L209" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M209" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx feat. xian</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N209" s="8" t="n">
+      <ns0:c r="M209" s="8" t="n">
         <ns0:v>13.1</ns0:v>
       </ns0:c>
-      <ns0:c r="P209" s="0" t="inlineStr">
+      <ns0:c r="R209" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>exdogma</ns0:t>
         </ns0:is>
@@ -12915,15 +12630,10 @@
       </ns0:c>
       <ns0:c r="L210" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>VOID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M210" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Seeing the void of RUIN</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N210" s="8" t="n">
+      <ns0:c r="M210" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -12971,7 +12681,7 @@
       <ns0:c r="K211" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P211" s="0" t="inlineStr">
+      <ns0:c r="R211" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Gravity Zone</ns0:t>
         </ns0:is>
@@ -13023,18 +12733,23 @@
       </ns0:c>
       <ns0:c r="L212" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M212" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>xian</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N212" s="8" t="n">
+      <ns0:c r="M212" s="8" t="n">
         <ns0:v>13.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P212" s="0" t="inlineStr">
+      <ns0:c r="N212" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">fgfgfgfgfgfg</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O212" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">藏(0.001)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R212" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Le Porteur dOmbre</ns0:t>
         </ns0:is>
@@ -13090,17 +12805,12 @@
       <ns0:c r="K213" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
-      <ns0:c r="L213" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M213" s="1" t="inlineStr">
+      <ns0:c r="N213" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>MNIess</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N213" s="8" t="inlineStr">
+      <ns0:c r="O213" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>β(0.001)</ns0:t>
         </ns0:is>
@@ -13158,15 +12868,10 @@
       </ns0:c>
       <ns0:c r="L214" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M214" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>光芒—寻找吾存在之证明—</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N214" s="8" t="n">
+      <ns0:c r="M214" s="8" t="n">
         <ns0:v>13.3</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -13220,7 +12925,7 @@
       <ns0:c r="K215" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P215" s="0" t="inlineStr">
+      <ns0:c r="R215" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>bexehendelta</ns0:t>
         </ns0:is>
@@ -13279,18 +12984,13 @@
       </ns0:c>
       <ns0:c r="L216" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M216" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>qqxqqx ＆ Nyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N216" s="8" t="n">
+      <ns0:c r="M216" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
-      <ns0:c r="P216" s="0" t="inlineStr">
+      <ns0:c r="R216" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>LunarParadoxx</ns0:t>
         </ns0:is>
@@ -13346,7 +13046,7 @@
       <ns0:c r="K217" s="8" t="n">
         <ns0:v>12.8</ns0:v>
       </ns0:c>
-      <ns0:c r="P217" s="0" t="inlineStr">
+      <ns0:c r="R217" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Dancing Flowers</ns0:t>
         </ns0:is>
@@ -13453,7 +13153,7 @@
       <ns0:c r="K219" s="13" t="n">
         <ns0:v>11.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P219" s="0" t="inlineStr">
+      <ns0:c r="R219" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>xu</ns0:t>
         </ns0:is>
@@ -13664,15 +13364,10 @@
       </ns0:c>
       <ns0:c r="L223" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M223" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>xian</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N223" s="8" t="n">
+      <ns0:c r="M223" s="8" t="n">
         <ns0:v>13.2</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -13828,7 +13523,7 @@
       <ns0:c r="K226" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P226" s="0" t="inlineStr">
+      <ns0:c r="R226" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>limen</ns0:t>
         </ns0:is>
@@ -13886,15 +13581,10 @@
       </ns0:c>
       <ns0:c r="L227" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M227" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>LOW-CROSS vs. oowoooowoo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N227" s="8" t="n">
+      <ns0:c r="M227" s="8" t="n">
         <ns0:v>13.4</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -13950,18 +13640,13 @@
       </ns0:c>
       <ns0:c r="L228" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M228" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>xmioalnsis</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N228" s="8" t="n">
+      <ns0:c r="M228" s="8" t="n">
         <ns0:v>13.7</ns0:v>
       </ns0:c>
-      <ns0:c r="P228" s="0" t="inlineStr">
+      <ns0:c r="R228" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Hemolesis</ns0:t>
         </ns0:is>
@@ -14068,7 +13753,7 @@
       <ns0:c r="K230" s="8" t="n">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P230" s="0" t="inlineStr">
+      <ns0:c r="R230" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Ether Vortex Final</ns0:t>
         </ns0:is>
@@ -14126,15 +13811,10 @@
       </ns0:c>
       <ns0:c r="L231" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M231" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Remaine_WH</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N231" s="8" t="n">
+      <ns0:c r="M231" s="8" t="n">
         <ns0:v>13.5</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -14184,15 +13864,10 @@
       </ns0:c>
       <ns0:c r="L232" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M232" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>metalslime___</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N232" s="8" t="n">
+      <ns0:c r="M232" s="8" t="n">
         <ns0:v>13.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -14248,15 +13923,10 @@
       </ns0:c>
       <ns0:c r="L233" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M233" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Berry Melodyの谱面挑战状</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N233" s="8" t="n">
+      <ns0:c r="M233" s="8" t="n">
         <ns0:v>13.8</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -14312,15 +13982,10 @@
       </ns0:c>
       <ns0:c r="L234" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M234" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>The Echoes of "M": Beyond Reality</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N234" s="8" t="n">
+      <ns0:c r="M234" s="8" t="n">
         <ns0:v>13.9</ns0:v>
       </ns0:c>
     </ns0:row>
@@ -14368,18 +14033,13 @@
       </ns0:c>
       <ns0:c r="L235" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M235" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Berry Melody Chart Team</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N235" s="8" t="n">
+      <ns0:c r="M235" s="8" t="n">
         <ns0:v>13.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P235" s="0" t="inlineStr">
+      <ns0:c r="R235" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>HeiBai</ns0:t>
         </ns0:is>
@@ -14437,18 +14097,13 @@
       </ns0:c>
       <ns0:c r="L236" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M236" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>Quetzai X vs. Nyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N236" s="8" t="n">
+      <ns0:c r="M236" s="8" t="n">
         <ns0:v>13.6</ns0:v>
       </ns0:c>
-      <ns0:c r="P236" s="0" t="inlineStr">
+      <ns0:c r="R236" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Maple Blade Twirling</ns0:t>
         </ns0:is>
@@ -14486,17 +14141,12 @@
       <ns0:c r="I237" s="8" t="n"/>
       <ns0:c r="J237" s="1" t="n"/>
       <ns0:c r="K237" s="8" t="n"/>
-      <ns0:c r="L237" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>FOOL</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M237" s="1" t="inlineStr">
+      <ns0:c r="P237" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Bro Way Studio</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N237" s="8" t="inlineStr">
+      <ns0:c r="Q237" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>4.1(0.001)</ns0:t>
         </ns0:is>
@@ -14534,28 +14184,23 @@
       <ns0:c r="I238" s="8" t="n"/>
       <ns0:c r="J238" s="1" t="n"/>
       <ns0:c r="K238" s="8" t="n"/>
-      <ns0:c r="L238" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DREAMY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M238" s="1" t="inlineStr">
+      <ns0:c r="N238" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Q.M.O.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N238" s="8" t="inlineStr">
+      <ns0:c r="O238" s="8" t="inlineStr">
         <ns0:is>
           <ns0:t>αβγ(0.001)</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="P238" s="0" t="inlineStr">
+      <ns0:c r="R238" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>KeLing is Flower</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="239" spans="1:16">
+    <ns0:row r="239" spans="1:17">
       <ns0:c r="A239" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>九蓮寶燈</ns0:t>
@@ -14595,13 +14240,13 @@
       <ns0:c r="K239" s="8">
         <ns0:v>12.9</ns0:v>
       </ns0:c>
-      <ns0:c r="P239" s="0" t="inlineStr">
+      <ns0:c r="R239" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>Nine Lights</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="240" spans="1:16">
+    <ns0:row r="240" spans="1:17">
       <ns0:c r="A240" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Cyber Attack</ns0:t>
@@ -14642,7 +14287,7 @@
         <ns0:v>12.4</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="241" spans="1:16">
+    <ns0:row r="241" spans="1:17">
       <ns0:c r="A241" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Ark</ns0:t>
@@ -14684,19 +14329,14 @@
       </ns0:c>
       <ns0:c r="L241" s="1" t="inlineStr">
         <ns0:is>
-          <ns0:t>RUIN</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M241" s="1" t="inlineStr">
-        <ns0:is>
           <ns0:t>MDTT</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="N241" s="8">
+      <ns0:c r="M241" s="8">
         <ns0:v>13.0</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="242" spans="1:16">
+    <ns0:row r="242" spans="1:17">
       <ns0:c r="A242" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Qamar</ns0:t>
@@ -14737,7 +14377,7 @@
         <ns0:v>12.0</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="243" spans="1:16">
+    <ns0:row r="243" spans="1:17">
       <ns0:c r="A243" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>Fuzzy-Navel</ns0:t>
@@ -14778,7 +14418,7 @@
         <ns0:v>11.6</ns0:v>
       </ns0:c>
     </ns0:row>
-    <ns0:row r="244" spans="1:16">
+    <ns0:row r="244" spans="1:17">
       <ns0:c r="A244" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>FRENZY☆SHINY</ns0:t>
@@ -14818,7 +14458,7 @@
       <ns0:c r="K244" s="8">
         <ns0:v>11.3</ns0:v>
       </ns0:c>
-      <ns0:c r="P244" s="0" t="inlineStr">
+      <ns0:c r="R244" s="0" t="inlineStr">
         <ns0:is>
           <ns0:t>FRENZYaSHINY</ns0:t>
         </ns0:is>

--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -1144,7 +1144,7 @@
     <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
     <ns0:pageSetUpPr/>
   </ns0:sheetPr>
-  <ns0:dimension ref="A1:P238"/>
+  <ns0:dimension ref="A1:R244"/>
   <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.25"/>
   <ns0:cols>
     <ns0:col width="36.7833333333333" customWidth="1" style="1" min="1" max="4"/>
@@ -4350,10 +4350,8 @@
           <ns0:t>Clementin</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I58" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>8,3</ns0:t>
-        </ns0:is>
+      <ns0:c r="I58" s="8" t="n">
+        <ns0:v>8.3</ns0:v>
       </ns0:c>
       <ns0:c r="J58" s="1" t="inlineStr">
         <ns0:is>
@@ -4462,7 +4460,11 @@
       <ns0:c r="G60" s="8" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="H60" s="1" t="n"/>
+      <ns0:c r="H60" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LOAO</ns0:t>
+        </ns0:is>
+      </ns0:c>
       <ns0:c r="I60" s="8" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
@@ -6012,8 +6014,14 @@
       <ns0:c r="G89" s="8" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="H89" s="1" t="n"/>
-      <ns0:c r="I89" s="8" t="n"/>
+      <ns0:c r="H89" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Twilight_morning</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I89" s="8" t="n">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
       <ns0:c r="J89" s="1" t="inlineStr">
         <ns0:is>
           <ns0:t>qqxqqx▲oowoo</ns0:t>
@@ -8893,10 +8901,8 @@
           <ns0:t>Nyo</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="I143" s="8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>9,9</ns0:t>
-        </ns0:is>
+      <ns0:c r="I143" s="8" t="n">
+        <ns0:v>9.9</ns0:v>
       </ns0:c>
       <ns0:c r="J143" s="1" t="inlineStr">
         <ns0:is>
@@ -13152,6 +13158,14 @@
       </ns0:c>
       <ns0:c r="K219" s="13" t="n">
         <ns0:v>11.6</ns0:v>
+      </ns0:c>
+      <ns0:c r="L219" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rIchArD in the Void</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M219" s="8" t="n">
+        <ns0:v>12.8</ns0:v>
       </ns0:c>
       <ns0:c r="R219" s="0" t="inlineStr">
         <ns0:is>
@@ -14464,9 +14478,153 @@
         </ns0:is>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="245" spans="1:16">
+      <ns0:c r="A245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Σquinoχ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ADA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>永恒指南针 feat.豆乳</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rchr</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G245" s="8">
+        <ns0:v>3.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rchr</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I245" s="8">
+        <ns0:v>8.3</ns0:v>
+      </ns0:c>
+      <ns0:c r="J245" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>sη_rιchάrδ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K245" s="8">
+        <ns0:v>12.7</ns0:v>
+      </ns0:c>
+      <ns0:c r="R245" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Equinox</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="246" spans="1:16">
+      <ns0:c r="A246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Recall Memories</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>uma</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>水沐汐</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>三石</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G246" s="8">
+        <ns0:v>5.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>南白 vs 三石</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I246" s="8">
+        <ns0:v>8.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="J246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>豆沙包aaa(充电中)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K246" s="8">
+        <ns0:v>12.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="L246" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>rIchArD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M246" s="8">
+        <ns0:v>12.8</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="247" spans="1:16">
+      <ns0:c r="A247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Tales of Misery</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ryhki</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>豆乳</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>亜師</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G247" s="8">
+        <ns0:v>4.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>亜師</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I247" s="8">
+        <ns0:v>9.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="J247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>亜師 ＆ qqxqqx</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K247" s="8">
+        <ns0:v>12.6</ns0:v>
+      </ns0:c>
+      <ns0:c r="L247" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LandNox</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M247" s="8">
+        <ns0:v>13.5</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:N239">
-    <ns0:sortState ref="A2:N239">
+  <ns0:autoFilter ref="A1:R244">
+    <ns0:sortState ref="A2:R244">
       <ns0:sortCondition ref="K1"/>
     </ns0:sortState>
   </ns0:autoFilter>

--- a/qwwshs/plugins/bm/constexcel.xlsx
+++ b/qwwshs/plugins/bm/constexcel.xlsx
@@ -14622,6 +14622,109 @@
         <ns0:v>13.5</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="248" spans="1:16">
+      <ns0:c r="A248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1NF3S+@+!0N</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DM DOKURO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>青岚柟</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>xian</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G248" s="8">
+        <ns0:v>7.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>xian</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I248" s="8">
+        <ns0:v>10.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="J248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Swimmingtalker</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K248" s="8">
+        <ns0:v>12.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="L248" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Xi!An</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M248" s="8">
+        <ns0:v>13.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="R248" s="0" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1NF3S0N</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="249" spans="1:16">
+      <ns0:c r="A249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Fly of Beelzebub</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DM DOKURO</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Frank_DL / 擦屁股的猫</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Remaine_WH被杀死了 凶手是瘟疫导弹</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G249" s="8">
+        <ns0:v>4.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Remaine_WH奴役了蜜蜂。</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I249" s="8">
+        <ns0:v>8.8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ICEbluebee_</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K249" s="8">
+        <ns0:v>12.5</ns0:v>
+      </ns0:c>
+      <ns0:c r="L249" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Fly of Beelzebub</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M249" s="8">
+        <ns0:v>13.2</ns0:v>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:autoFilter ref="A1:R244">
     <ns0:sortState ref="A2:R244">
